--- a/B-pojat.xlsx
+++ b/B-pojat.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\own_prog\github\kaudet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6B6E0E6-BCFD-4535-9DF5-232A27A66125}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9605BEAD-C0B7-46EF-9043-65AA102B0B9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3048" yWindow="1392" windowWidth="19104" windowHeight="11892" tabRatio="880" xr2:uid="{CFC6D258-5D3C-46F8-BFEC-F3C271445404}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="880" activeTab="1" xr2:uid="{CFC6D258-5D3C-46F8-BFEC-F3C271445404}"/>
   </bookViews>
   <sheets>
     <sheet name="B 2023-2027" sheetId="10" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="150">
   <si>
     <t>päivä</t>
   </si>
@@ -484,6 +484,12 @@
   </si>
   <si>
     <t>PuMa 2</t>
+  </si>
+  <si>
+    <t>19-25,16-25</t>
+  </si>
+  <si>
+    <t>21-25,11-25</t>
   </si>
 </sst>
 </file>
@@ -1125,11 +1131,11 @@
       </c>
       <c r="C5" s="23">
         <f>'B 2026-2027'!R2</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5" s="23">
         <f>'B 2026-2027'!O2</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" s="23">
         <f>'B 2026-2027'!P2</f>
@@ -1141,7 +1147,7 @@
       </c>
       <c r="G5" s="23">
         <f>'B 2026-2027'!O2</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" s="23">
         <f>'B 2026-2027'!Q2</f>
@@ -1149,7 +1155,7 @@
       </c>
       <c r="I5" s="23">
         <f>'B 2026-2027'!O2</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="23">
         <f>'B 2026-2027'!Q2</f>
@@ -1164,11 +1170,11 @@
       </c>
       <c r="C6" s="24">
         <f>SUM(C2:C5)</f>
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D6" s="24">
         <f t="shared" ref="D6:J6" si="0">SUM(D2:D5)</f>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E6" s="24">
         <f t="shared" si="0"/>
@@ -1180,7 +1186,7 @@
       </c>
       <c r="G6" s="24">
         <f t="shared" si="0"/>
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H6" s="24">
         <f t="shared" si="0"/>
@@ -1188,7 +1194,7 @@
       </c>
       <c r="I6" s="24">
         <f t="shared" si="0"/>
-        <v>3460</v>
+        <v>3461</v>
       </c>
       <c r="J6" s="24">
         <f t="shared" si="0"/>
@@ -1279,21 +1285,31 @@
       <c r="D2" s="14" t="s">
         <v>146</v>
       </c>
-      <c r="E2" s="15"/>
-      <c r="F2" s="14"/>
+      <c r="E2" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>148</v>
+      </c>
       <c r="G2" s="14"/>
       <c r="H2" s="14"/>
       <c r="I2" s="14"/>
-      <c r="J2" s="14"/>
-      <c r="K2" s="14"/>
-      <c r="L2" s="14"/>
+      <c r="J2" s="14">
+        <v>0</v>
+      </c>
+      <c r="K2" s="14">
+        <v>35</v>
+      </c>
+      <c r="L2" s="14">
+        <v>50</v>
+      </c>
       <c r="M2" s="14"/>
       <c r="N2" s="17" t="s">
         <v>9</v>
       </c>
       <c r="O2" s="14">
         <f>SUM(H2:H24)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2" s="14">
         <f>SUM(I10:I13)</f>
@@ -1305,11 +1321,11 @@
       </c>
       <c r="R2" s="14">
         <f>SUM(O2:Q2)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S2" s="14">
         <f>R2*2</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
@@ -1325,21 +1341,31 @@
       <c r="D3" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="E3" s="12"/>
-      <c r="F3" s="11"/>
+      <c r="E3" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>54</v>
+      </c>
       <c r="G3" s="11"/>
-      <c r="H3" s="11"/>
+      <c r="H3" s="11">
+        <v>1</v>
+      </c>
       <c r="I3" s="11"/>
       <c r="J3" s="11"/>
-      <c r="K3" s="11"/>
-      <c r="L3" s="11"/>
+      <c r="K3" s="11">
+        <v>50</v>
+      </c>
+      <c r="L3" s="11">
+        <v>43</v>
+      </c>
       <c r="M3" s="11"/>
       <c r="N3" s="18" t="s">
         <v>4</v>
       </c>
       <c r="O3" s="11">
         <f>SUM(H2:H24)*2+SUM(I2:I24)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P3" s="11"/>
       <c r="Q3" s="11">
@@ -1348,7 +1374,7 @@
       </c>
       <c r="R3" s="11">
         <f>SUM(O3:Q3)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S3" s="11"/>
     </row>
@@ -1365,30 +1391,40 @@
       <c r="D4" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="E4" s="15"/>
-      <c r="F4" s="14"/>
+      <c r="E4" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="14" t="s">
+        <v>149</v>
+      </c>
       <c r="G4" s="14"/>
       <c r="H4" s="14"/>
       <c r="I4" s="14"/>
-      <c r="J4" s="14"/>
-      <c r="K4" s="14"/>
-      <c r="L4" s="14"/>
+      <c r="J4" s="14">
+        <v>0</v>
+      </c>
+      <c r="K4" s="14">
+        <v>32</v>
+      </c>
+      <c r="L4" s="14">
+        <v>60</v>
+      </c>
       <c r="M4" s="14"/>
       <c r="N4" s="17" t="s">
         <v>12</v>
       </c>
       <c r="O4" s="14">
         <f>SUM(K2:K24)</f>
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="P4" s="14"/>
       <c r="Q4" s="14">
         <f>SUM(L2:L24)</f>
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="R4" s="14">
         <f>SUM(O4:Q4)</f>
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="S4" s="14"/>
     </row>

--- a/B-pojat.xlsx
+++ b/B-pojat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\own_prog\github\kaudet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9605BEAD-C0B7-46EF-9043-65AA102B0B9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D32DAF35-60A7-4DE3-855C-6E76E277F26C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="880" activeTab="1" xr2:uid="{CFC6D258-5D3C-46F8-BFEC-F3C271445404}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="155">
   <si>
     <t>päivä</t>
   </si>
@@ -490,6 +490,21 @@
   </si>
   <si>
     <t>21-25,11-25</t>
+  </si>
+  <si>
+    <t>16.10.2026</t>
+  </si>
+  <si>
+    <t>7.11.2026</t>
+  </si>
+  <si>
+    <t>VaLePa P11</t>
+  </si>
+  <si>
+    <t>Jankko 2</t>
+  </si>
+  <si>
+    <t>LaihLu</t>
   </si>
 </sst>
 </file>
@@ -581,7 +596,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -635,6 +650,9 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1273,8 +1291,8 @@
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A2" s="13">
-        <v>46312</v>
+      <c r="A2" s="15" t="s">
+        <v>150</v>
       </c>
       <c r="B2" s="14" t="s">
         <v>7</v>
@@ -1329,8 +1347,8 @@
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A3" s="20">
-        <v>46312</v>
+      <c r="A3" s="25" t="s">
+        <v>150</v>
       </c>
       <c r="B3" s="12" t="s">
         <v>7</v>
@@ -1379,8 +1397,8 @@
       <c r="S3" s="11"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A4" s="13">
-        <v>46312</v>
+      <c r="A4" s="15" t="s">
+        <v>150</v>
       </c>
       <c r="B4" s="14" t="s">
         <v>7</v>
@@ -1429,10 +1447,18 @@
       <c r="S4" s="14"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A5" s="10"/>
-      <c r="B5" s="11"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11"/>
+      <c r="A5" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>152</v>
+      </c>
       <c r="E5" s="12"/>
       <c r="F5" s="11"/>
       <c r="G5" s="11"/>
@@ -1450,10 +1476,18 @@
       <c r="S5" s="11"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A6" s="13"/>
-      <c r="B6" s="14"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
+      <c r="A6" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>153</v>
+      </c>
       <c r="E6" s="15"/>
       <c r="F6" s="14"/>
       <c r="G6" s="14"/>
@@ -1471,10 +1505,18 @@
       <c r="S6" s="14"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A7" s="10"/>
-      <c r="B7" s="11"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
+      <c r="A7" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>154</v>
+      </c>
       <c r="E7" s="12"/>
       <c r="F7" s="11"/>
       <c r="G7" s="11"/>
@@ -1492,7 +1534,7 @@
       <c r="S7" s="11"/>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A8" s="13"/>
+      <c r="A8" s="15"/>
       <c r="B8" s="14"/>
       <c r="C8" s="14"/>
       <c r="D8" s="14"/>
@@ -1513,7 +1555,7 @@
       <c r="S8" s="14"/>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A9" s="20"/>
+      <c r="A9" s="25"/>
       <c r="B9" s="21"/>
       <c r="C9" s="21"/>
       <c r="D9" s="11"/>
@@ -1534,7 +1576,7 @@
       <c r="S9" s="11"/>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A10" s="13"/>
+      <c r="A10" s="15"/>
       <c r="B10" s="14"/>
       <c r="C10" s="14"/>
       <c r="D10" s="14"/>
@@ -1555,7 +1597,7 @@
       <c r="S10" s="14"/>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A11" s="10"/>
+      <c r="A11" s="12"/>
       <c r="B11" s="11"/>
       <c r="C11" s="11"/>
       <c r="D11" s="11"/>
@@ -1576,7 +1618,7 @@
       <c r="S11" s="11"/>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A12" s="13"/>
+      <c r="A12" s="15"/>
       <c r="B12" s="14"/>
       <c r="C12" s="14"/>
       <c r="D12" s="14"/>
@@ -1597,7 +1639,7 @@
       <c r="S12" s="14"/>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A13" s="10"/>
+      <c r="A13" s="12"/>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -1618,7 +1660,7 @@
       <c r="S13" s="11"/>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A14" s="13"/>
+      <c r="A14" s="15"/>
       <c r="B14" s="14"/>
       <c r="C14" s="14"/>
       <c r="D14" s="14"/>
@@ -1639,7 +1681,7 @@
       <c r="S14" s="14"/>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A15" s="20"/>
+      <c r="A15" s="25"/>
       <c r="B15" s="21"/>
       <c r="C15" s="21"/>
       <c r="D15" s="11"/>
@@ -1660,7 +1702,7 @@
       <c r="S15" s="11"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A16" s="13"/>
+      <c r="A16" s="15"/>
       <c r="B16" s="14"/>
       <c r="C16" s="14"/>
       <c r="D16" s="14"/>
@@ -1681,7 +1723,7 @@
       <c r="S16" s="14"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A17" s="20"/>
+      <c r="A17" s="25"/>
       <c r="B17" s="21"/>
       <c r="C17" s="21"/>
       <c r="D17" s="11"/>
@@ -1702,7 +1744,7 @@
       <c r="S17" s="11"/>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A18" s="13"/>
+      <c r="A18" s="15"/>
       <c r="B18" s="14"/>
       <c r="C18" s="14"/>
       <c r="D18" s="14"/>
@@ -1723,7 +1765,7 @@
       <c r="S18" s="14"/>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A19" s="10"/>
+      <c r="A19" s="12"/>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
       <c r="D19" s="11"/>
@@ -1744,7 +1786,7 @@
       <c r="S19" s="11"/>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A20" s="13"/>
+      <c r="A20" s="15"/>
       <c r="B20" s="14"/>
       <c r="C20" s="14"/>
       <c r="D20" s="14"/>
@@ -1765,7 +1807,7 @@
       <c r="S20" s="14"/>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A21" s="10"/>
+      <c r="A21" s="12"/>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
       <c r="D21" s="11"/>
@@ -1786,7 +1828,7 @@
       <c r="S21" s="11"/>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A22" s="13"/>
+      <c r="A22" s="15"/>
       <c r="B22" s="14"/>
       <c r="C22" s="14"/>
       <c r="D22" s="14"/>
@@ -1807,7 +1849,7 @@
       <c r="S22" s="14"/>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A23" s="10"/>
+      <c r="A23" s="12"/>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
       <c r="D23" s="11"/>
@@ -1828,7 +1870,7 @@
       <c r="S23" s="11"/>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A24" s="13"/>
+      <c r="A24" s="15"/>
       <c r="B24" s="14"/>
       <c r="C24" s="14"/>
       <c r="D24" s="14"/>
